--- a/pages/Valores_maximos_P_meses.xlsx
+++ b/pages/Valores_maximos_P_meses.xlsx
@@ -653,13 +653,13 @@
         <v>2102</v>
       </c>
       <c r="P3" t="n">
-        <v>2107</v>
+        <v>2131</v>
       </c>
       <c r="Q3" t="n">
-        <v>2107</v>
+        <v>2131</v>
       </c>
       <c r="R3" t="n">
-        <v>33.71</v>
+        <v>34.1</v>
       </c>
       <c r="S3" t="n">
         <v>8</v>
@@ -1165,13 +1165,13 @@
         <v>1036</v>
       </c>
       <c r="P11" t="n">
-        <v>1077</v>
+        <v>1539</v>
       </c>
       <c r="Q11" t="n">
-        <v>1077</v>
+        <v>1539</v>
       </c>
       <c r="R11" t="n">
-        <v>35.9</v>
+        <v>51.3</v>
       </c>
       <c r="S11" t="n">
         <v>8</v>
@@ -1375,13 +1375,13 @@
         <v>12165</v>
       </c>
       <c r="P14" t="n">
-        <v>13113</v>
+        <v>14796</v>
       </c>
       <c r="Q14" t="n">
-        <v>14496</v>
+        <v>14796</v>
       </c>
       <c r="R14" t="n">
-        <v>57.98</v>
+        <v>59.18</v>
       </c>
       <c r="S14" t="n">
         <v>8</v>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>299</v>
+        <v>1520</v>
       </c>
       <c r="Q15" t="n">
         <v>4925</v>
@@ -1515,7 +1515,7 @@
         <v>14925</v>
       </c>
       <c r="P16" t="n">
-        <v>14574</v>
+        <v>15851</v>
       </c>
       <c r="Q16" t="n">
         <v>28370</v>
@@ -2027,13 +2027,13 @@
         <v>9466</v>
       </c>
       <c r="P24" t="n">
-        <v>9373</v>
+        <v>9471</v>
       </c>
       <c r="Q24" t="n">
-        <v>9466</v>
+        <v>9471</v>
       </c>
       <c r="R24" t="n">
-        <v>75.73</v>
+        <v>75.77</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -2283,7 +2283,7 @@
         <v>12217</v>
       </c>
       <c r="P28" t="n">
-        <v>12017</v>
+        <v>12085</v>
       </c>
       <c r="Q28" t="n">
         <v>12217</v>
@@ -2701,13 +2701,13 @@
         <v>2175</v>
       </c>
       <c r="P35" t="n">
-        <v>2251</v>
+        <v>2265</v>
       </c>
       <c r="Q35" t="n">
-        <v>2251</v>
+        <v>2265</v>
       </c>
       <c r="R35" t="n">
-        <v>75.03</v>
+        <v>75.5</v>
       </c>
       <c r="S35" t="n">
         <v>8</v>
@@ -3377,13 +3377,13 @@
         <v>3477</v>
       </c>
       <c r="P45" t="n">
-        <v>4333</v>
+        <v>4079</v>
       </c>
       <c r="Q45" t="n">
-        <v>4333</v>
+        <v>4079</v>
       </c>
       <c r="R45" t="n">
-        <v>28.89</v>
+        <v>27.19</v>
       </c>
       <c r="S45" t="n">
         <v>8</v>
@@ -4937,7 +4937,7 @@
         <v>12752</v>
       </c>
       <c r="P69" t="n">
-        <v>11592</v>
+        <v>11158</v>
       </c>
       <c r="Q69" t="n">
         <v>12752</v>
@@ -5007,13 +5007,13 @@
         <v>19630</v>
       </c>
       <c r="P70" t="n">
-        <v>23482</v>
+        <v>24431</v>
       </c>
       <c r="Q70" t="n">
-        <v>23482</v>
+        <v>24431</v>
       </c>
       <c r="R70" t="n">
-        <v>93.93000000000001</v>
+        <v>97.72</v>
       </c>
       <c r="S70" t="n">
         <v>8</v>
@@ -5473,13 +5473,13 @@
         <v>19559</v>
       </c>
       <c r="P77" t="n">
-        <v>22207</v>
+        <v>24841</v>
       </c>
       <c r="Q77" t="n">
-        <v>22207</v>
+        <v>24841</v>
       </c>
       <c r="R77" t="n">
-        <v>49.35</v>
+        <v>55.2</v>
       </c>
       <c r="S77" t="n">
         <v>8</v>
@@ -6173,13 +6173,13 @@
         <v>3914</v>
       </c>
       <c r="P87" t="n">
-        <v>4095</v>
+        <v>3534</v>
       </c>
       <c r="Q87" t="n">
-        <v>4095</v>
+        <v>3914</v>
       </c>
       <c r="R87" t="n">
-        <v>54.6</v>
+        <v>52.19</v>
       </c>
       <c r="S87" t="n">
         <v>8</v>
@@ -6965,7 +6965,7 @@
         <v>3522</v>
       </c>
       <c r="P99" t="n">
-        <v>3348</v>
+        <v>3414</v>
       </c>
       <c r="Q99" t="n">
         <v>3576</v>
@@ -7361,7 +7361,7 @@
         <v>27513</v>
       </c>
       <c r="P105" t="n">
-        <v>13866</v>
+        <v>12281</v>
       </c>
       <c r="Q105" t="n">
         <v>27513</v>
@@ -7431,7 +7431,7 @@
         <v>9607</v>
       </c>
       <c r="P106" t="n">
-        <v>3616</v>
+        <v>2863</v>
       </c>
       <c r="Q106" t="n">
         <v>9607</v>
@@ -7617,7 +7617,7 @@
         <v>14456</v>
       </c>
       <c r="P109" t="n">
-        <v>13449</v>
+        <v>14217</v>
       </c>
       <c r="Q109" t="n">
         <v>14508</v>
@@ -8221,13 +8221,13 @@
         <v>12244</v>
       </c>
       <c r="P119" t="n">
-        <v>14144</v>
+        <v>11188</v>
       </c>
       <c r="Q119" t="n">
-        <v>14144</v>
+        <v>14086</v>
       </c>
       <c r="R119" t="n">
-        <v>56.58</v>
+        <v>56.34</v>
       </c>
       <c r="S119" t="n">
         <v>8</v>
@@ -8617,13 +8617,13 @@
         <v>26571</v>
       </c>
       <c r="P125" t="n">
-        <v>27375</v>
+        <v>28173</v>
       </c>
       <c r="Q125" t="n">
-        <v>27375</v>
+        <v>28173</v>
       </c>
       <c r="R125" t="n">
-        <v>109.5</v>
+        <v>112.69</v>
       </c>
       <c r="S125" t="n">
         <v>8</v>
@@ -9293,7 +9293,7 @@
         <v>6372</v>
       </c>
       <c r="P135" t="n">
-        <v>1643</v>
+        <v>1801</v>
       </c>
       <c r="Q135" t="n">
         <v>9526</v>
@@ -9525,13 +9525,13 @@
         <v>22643</v>
       </c>
       <c r="P139" t="n">
-        <v>23453</v>
+        <v>23750</v>
       </c>
       <c r="Q139" t="n">
-        <v>23453</v>
+        <v>23750</v>
       </c>
       <c r="R139" t="n">
-        <v>93.81</v>
+        <v>95</v>
       </c>
       <c r="S139" t="n">
         <v>8</v>
@@ -9665,7 +9665,7 @@
         <v>4729</v>
       </c>
       <c r="P141" t="n">
-        <v>4977</v>
+        <v>5101</v>
       </c>
       <c r="Q141" t="n">
         <v>5336</v>
@@ -10335,7 +10335,7 @@
         <v>4276</v>
       </c>
       <c r="P151" t="n">
-        <v>4046</v>
+        <v>4144</v>
       </c>
       <c r="Q151" t="n">
         <v>4768</v>
@@ -11383,13 +11383,13 @@
         <v>11635</v>
       </c>
       <c r="P167" t="n">
-        <v>11893</v>
+        <v>11975</v>
       </c>
       <c r="Q167" t="n">
-        <v>11893</v>
+        <v>11975</v>
       </c>
       <c r="R167" t="n">
-        <v>47.57</v>
+        <v>47.9</v>
       </c>
       <c r="S167" t="n">
         <v>8</v>
@@ -11453,13 +11453,13 @@
         <v>2788</v>
       </c>
       <c r="P168" t="n">
-        <v>2764</v>
+        <v>3495</v>
       </c>
       <c r="Q168" t="n">
-        <v>2788</v>
+        <v>3495</v>
       </c>
       <c r="R168" t="n">
-        <v>29.74</v>
+        <v>37.28</v>
       </c>
       <c r="S168" t="n">
         <v>8</v>
@@ -11871,7 +11871,7 @@
         <v>6068</v>
       </c>
       <c r="P175" t="n">
-        <v>3247</v>
+        <v>2762</v>
       </c>
       <c r="Q175" t="n">
         <v>6068</v>
@@ -12011,7 +12011,7 @@
         <v>19578</v>
       </c>
       <c r="P177" t="n">
-        <v>15584</v>
+        <v>16659</v>
       </c>
       <c r="Q177" t="n">
         <v>19578</v>
@@ -12641,7 +12641,7 @@
         <v>19286</v>
       </c>
       <c r="P186" t="n">
-        <v>16782</v>
+        <v>17525</v>
       </c>
       <c r="Q186" t="n">
         <v>23208</v>
@@ -12781,7 +12781,7 @@
         <v>26734</v>
       </c>
       <c r="P188" t="n">
-        <v>24093</v>
+        <v>27216</v>
       </c>
       <c r="Q188" t="n">
         <v>27359</v>
@@ -14387,7 +14387,7 @@
         <v>12128</v>
       </c>
       <c r="P213" t="n">
-        <v>11874</v>
+        <v>11883</v>
       </c>
       <c r="Q213" t="n">
         <v>12128</v>
@@ -14457,7 +14457,7 @@
         <v>13013</v>
       </c>
       <c r="P214" t="n">
-        <v>12581</v>
+        <v>12753</v>
       </c>
       <c r="Q214" t="n">
         <v>13013</v>
@@ -14853,7 +14853,7 @@
         <v>2047</v>
       </c>
       <c r="P220" t="n">
-        <v>1876</v>
+        <v>1927</v>
       </c>
       <c r="Q220" t="n">
         <v>2306</v>
@@ -15249,7 +15249,7 @@
         <v>27054</v>
       </c>
       <c r="P226" t="n">
-        <v>23057</v>
+        <v>23717</v>
       </c>
       <c r="Q226" t="n">
         <v>27054</v>
@@ -15715,7 +15715,7 @@
         <v>6622</v>
       </c>
       <c r="P233" t="n">
-        <v>5941</v>
+        <v>5991</v>
       </c>
       <c r="Q233" t="n">
         <v>6622</v>
@@ -15995,13 +15995,13 @@
         <v>1844</v>
       </c>
       <c r="P237" t="n">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="Q237" t="n">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="R237" t="n">
-        <v>46.39</v>
+        <v>46.44</v>
       </c>
       <c r="S237" t="n">
         <v>8</v>
@@ -16345,7 +16345,7 @@
         <v>7078</v>
       </c>
       <c r="P242" t="n">
-        <v>6784</v>
+        <v>5819</v>
       </c>
       <c r="Q242" t="n">
         <v>7078</v>
@@ -16415,7 +16415,7 @@
         <v>7330</v>
       </c>
       <c r="P243" t="n">
-        <v>6332</v>
+        <v>5618</v>
       </c>
       <c r="Q243" t="n">
         <v>7330</v>
@@ -16485,7 +16485,7 @@
         <v>3733</v>
       </c>
       <c r="P244" t="n">
-        <v>3226</v>
+        <v>2643</v>
       </c>
       <c r="Q244" t="n">
         <v>3733</v>
@@ -16555,7 +16555,7 @@
         <v>3899</v>
       </c>
       <c r="P245" t="n">
-        <v>3379</v>
+        <v>2850</v>
       </c>
       <c r="Q245" t="n">
         <v>3899</v>
@@ -16695,13 +16695,13 @@
         <v>4579</v>
       </c>
       <c r="P247" t="n">
-        <v>5033</v>
+        <v>4199</v>
       </c>
       <c r="Q247" t="n">
-        <v>5033</v>
+        <v>4579</v>
       </c>
       <c r="R247" t="n">
-        <v>50.13</v>
+        <v>45.61</v>
       </c>
       <c r="S247" t="n">
         <v>8</v>
@@ -17045,13 +17045,13 @@
         <v>2187</v>
       </c>
       <c r="P252" t="n">
-        <v>2445</v>
+        <v>2499</v>
       </c>
       <c r="Q252" t="n">
-        <v>2445</v>
+        <v>2499</v>
       </c>
       <c r="R252" t="n">
-        <v>51.15</v>
+        <v>52.28</v>
       </c>
       <c r="S252" t="n">
         <v>8</v>
@@ -17185,7 +17185,7 @@
         <v>1797</v>
       </c>
       <c r="P254" t="n">
-        <v>1215</v>
+        <v>1051</v>
       </c>
       <c r="Q254" t="n">
         <v>1930</v>
@@ -17465,7 +17465,7 @@
         <v>5648</v>
       </c>
       <c r="P258" t="n">
-        <v>5424</v>
+        <v>5437</v>
       </c>
       <c r="Q258" t="n">
         <v>5648</v>
@@ -17605,7 +17605,7 @@
         <v>1054</v>
       </c>
       <c r="P260" t="n">
-        <v>1009</v>
+        <v>1038</v>
       </c>
       <c r="Q260" t="n">
         <v>1371</v>
@@ -17675,7 +17675,7 @@
         <v>2164</v>
       </c>
       <c r="P261" t="n">
-        <v>1838</v>
+        <v>1993</v>
       </c>
       <c r="Q261" t="n">
         <v>3044</v>
@@ -17745,13 +17745,13 @@
         <v>4353</v>
       </c>
       <c r="P262" t="n">
-        <v>4488</v>
+        <v>4533</v>
       </c>
       <c r="Q262" t="n">
-        <v>4488</v>
+        <v>4533</v>
       </c>
       <c r="R262" t="n">
-        <v>89.41</v>
+        <v>90.31</v>
       </c>
       <c r="S262" t="n">
         <v>8</v>
@@ -17955,13 +17955,13 @@
         <v>6086</v>
       </c>
       <c r="P265" t="n">
-        <v>6309</v>
+        <v>6514</v>
       </c>
       <c r="Q265" t="n">
-        <v>6309</v>
+        <v>6514</v>
       </c>
       <c r="R265" t="n">
-        <v>78.86</v>
+        <v>81.42</v>
       </c>
       <c r="S265" t="n">
         <v>8</v>
@@ -18025,7 +18025,7 @@
         <v>5986</v>
       </c>
       <c r="P266" t="n">
-        <v>5695</v>
+        <v>6519</v>
       </c>
       <c r="Q266" t="n">
         <v>7429</v>
@@ -18095,13 +18095,13 @@
         <v>2312</v>
       </c>
       <c r="P267" t="n">
-        <v>2398</v>
+        <v>2428</v>
       </c>
       <c r="Q267" t="n">
-        <v>2398</v>
+        <v>2428</v>
       </c>
       <c r="R267" t="n">
-        <v>59.95</v>
+        <v>60.7</v>
       </c>
       <c r="S267" t="n">
         <v>8</v>
@@ -18445,7 +18445,7 @@
         <v>4999</v>
       </c>
       <c r="P272" t="n">
-        <v>5018</v>
+        <v>5031</v>
       </c>
       <c r="Q272" t="n">
         <v>5324</v>
@@ -18515,7 +18515,7 @@
         <v>4413</v>
       </c>
       <c r="P273" t="n">
-        <v>4307</v>
+        <v>4400</v>
       </c>
       <c r="Q273" t="n">
         <v>4413</v>
@@ -18585,7 +18585,7 @@
         <v>4586</v>
       </c>
       <c r="P274" t="n">
-        <v>5097</v>
+        <v>4991</v>
       </c>
       <c r="Q274" t="n">
         <v>8427</v>
@@ -18981,7 +18981,7 @@
         <v>84</v>
       </c>
       <c r="P280" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="Q280" t="n">
         <v>807</v>
@@ -19051,7 +19051,7 @@
         <v>886</v>
       </c>
       <c r="P281" t="n">
-        <v>914</v>
+        <v>829</v>
       </c>
       <c r="Q281" t="n">
         <v>2450</v>
@@ -19121,13 +19121,13 @@
         <v>5453</v>
       </c>
       <c r="P282" t="n">
-        <v>5710</v>
+        <v>5717</v>
       </c>
       <c r="Q282" t="n">
-        <v>5710</v>
+        <v>5717</v>
       </c>
       <c r="R282" t="n">
-        <v>79.63</v>
+        <v>79.73</v>
       </c>
       <c r="S282" t="n">
         <v>8</v>
@@ -19471,7 +19471,7 @@
         <v>3215</v>
       </c>
       <c r="P287" t="n">
-        <v>3051</v>
+        <v>3080</v>
       </c>
       <c r="Q287" t="n">
         <v>3215</v>
@@ -19703,13 +19703,13 @@
         <v>664</v>
       </c>
       <c r="P291" t="n">
-        <v>684</v>
+        <v>734</v>
       </c>
       <c r="Q291" t="n">
-        <v>684</v>
+        <v>734</v>
       </c>
       <c r="R291" t="n">
-        <v>28.62</v>
+        <v>30.71</v>
       </c>
       <c r="S291" t="n">
         <v>8</v>
@@ -19843,13 +19843,13 @@
         <v>2181</v>
       </c>
       <c r="P293" t="n">
-        <v>2249</v>
+        <v>2268</v>
       </c>
       <c r="Q293" t="n">
-        <v>2249</v>
+        <v>2268</v>
       </c>
       <c r="R293" t="n">
-        <v>74.97</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="S293" t="n">
         <v>8</v>
@@ -19913,7 +19913,7 @@
         <v>250</v>
       </c>
       <c r="P294" t="n">
-        <v>248</v>
+        <v>492</v>
       </c>
       <c r="Q294" t="n">
         <v>874</v>
@@ -21033,13 +21033,13 @@
         <v>3754</v>
       </c>
       <c r="P310" t="n">
-        <v>4124</v>
+        <v>3696</v>
       </c>
       <c r="Q310" t="n">
-        <v>4124</v>
+        <v>3754</v>
       </c>
       <c r="R310" t="n">
-        <v>41.24</v>
+        <v>37.54</v>
       </c>
       <c r="S310" t="n">
         <v>8</v>
@@ -22475,13 +22475,13 @@
         <v>4717</v>
       </c>
       <c r="P333" t="n">
-        <v>4813</v>
+        <v>5115</v>
       </c>
       <c r="Q333" t="n">
-        <v>4879</v>
+        <v>5115</v>
       </c>
       <c r="R333" t="n">
-        <v>48.79</v>
+        <v>51.15</v>
       </c>
       <c r="S333" t="n">
         <v>8</v>
@@ -22545,13 +22545,13 @@
         <v>5311</v>
       </c>
       <c r="P334" t="n">
-        <v>6185</v>
+        <v>6850</v>
       </c>
       <c r="Q334" t="n">
-        <v>6185</v>
+        <v>6850</v>
       </c>
       <c r="R334" t="n">
-        <v>51.54</v>
+        <v>57.08</v>
       </c>
       <c r="S334" t="n">
         <v>8</v>
@@ -22825,7 +22825,7 @@
         <v>4083</v>
       </c>
       <c r="P338" t="n">
-        <v>4005</v>
+        <v>4013</v>
       </c>
       <c r="Q338" t="n">
         <v>4083</v>
@@ -23523,13 +23523,13 @@
         <v>6030</v>
       </c>
       <c r="P349" t="n">
-        <v>9101</v>
+        <v>7979</v>
       </c>
       <c r="Q349" t="n">
-        <v>9101</v>
+        <v>7979</v>
       </c>
       <c r="R349" t="n">
-        <v>90.66</v>
+        <v>79.48</v>
       </c>
       <c r="S349" t="n">
         <v>8</v>
@@ -23663,7 +23663,7 @@
         <v>2641</v>
       </c>
       <c r="P351" t="n">
-        <v>3225</v>
+        <v>2962</v>
       </c>
       <c r="Q351" t="n">
         <v>4698</v>
@@ -24363,13 +24363,13 @@
         <v>2223</v>
       </c>
       <c r="P361" t="n">
-        <v>2106</v>
+        <v>2702</v>
       </c>
       <c r="Q361" t="n">
-        <v>2223</v>
+        <v>2702</v>
       </c>
       <c r="R361" t="n">
-        <v>22.23</v>
+        <v>27.02</v>
       </c>
       <c r="S361" t="n">
         <v>8</v>
@@ -25273,13 +25273,13 @@
         <v>3531</v>
       </c>
       <c r="P374" t="n">
-        <v>5346</v>
+        <v>5100</v>
       </c>
       <c r="Q374" t="n">
-        <v>5346</v>
+        <v>5100</v>
       </c>
       <c r="R374" t="n">
-        <v>53.46</v>
+        <v>51</v>
       </c>
       <c r="S374" t="n">
         <v>8</v>
@@ -25483,13 +25483,13 @@
         <v>6423</v>
       </c>
       <c r="P377" t="n">
-        <v>4894</v>
+        <v>6448</v>
       </c>
       <c r="Q377" t="n">
-        <v>6423</v>
+        <v>6448</v>
       </c>
       <c r="R377" t="n">
-        <v>53.52</v>
+        <v>53.73</v>
       </c>
       <c r="S377" t="n">
         <v>8</v>
@@ -25553,13 +25553,13 @@
         <v>6570</v>
       </c>
       <c r="P378" t="n">
-        <v>7077</v>
+        <v>7173</v>
       </c>
       <c r="Q378" t="n">
-        <v>7077</v>
+        <v>7173</v>
       </c>
       <c r="R378" t="n">
-        <v>58.98</v>
+        <v>59.78</v>
       </c>
       <c r="S378" t="n">
         <v>8</v>
@@ -25623,7 +25623,7 @@
         <v>5910</v>
       </c>
       <c r="P379" t="n">
-        <v>5163</v>
+        <v>5369</v>
       </c>
       <c r="Q379" t="n">
         <v>5910</v>
@@ -26253,13 +26253,13 @@
         <v>2537</v>
       </c>
       <c r="P388" t="n">
-        <v>2486</v>
+        <v>2905</v>
       </c>
       <c r="Q388" t="n">
-        <v>2537</v>
+        <v>2905</v>
       </c>
       <c r="R388" t="n">
-        <v>42.46</v>
+        <v>48.61</v>
       </c>
       <c r="S388" t="n">
         <v>8</v>
@@ -26323,7 +26323,7 @@
         <v>7403</v>
       </c>
       <c r="P389" t="n">
-        <v>6105</v>
+        <v>5593</v>
       </c>
       <c r="Q389" t="n">
         <v>7403</v>
@@ -26393,13 +26393,13 @@
         <v>2485</v>
       </c>
       <c r="P390" t="n">
-        <v>2886</v>
+        <v>2971</v>
       </c>
       <c r="Q390" t="n">
-        <v>2886</v>
+        <v>2971</v>
       </c>
       <c r="R390" t="n">
-        <v>28.86</v>
+        <v>29.71</v>
       </c>
       <c r="S390" t="n">
         <v>8</v>
@@ -26463,13 +26463,13 @@
         <v>172</v>
       </c>
       <c r="P391" t="n">
-        <v>1133</v>
+        <v>698</v>
       </c>
       <c r="Q391" t="n">
-        <v>1133</v>
+        <v>698</v>
       </c>
       <c r="R391" t="n">
-        <v>11.33</v>
+        <v>6.98</v>
       </c>
       <c r="S391" t="n">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>5981</v>
       </c>
       <c r="P393" t="n">
-        <v>5776</v>
+        <v>5627</v>
       </c>
       <c r="Q393" t="n">
         <v>5981</v>
@@ -26673,13 +26673,13 @@
         <v>1037</v>
       </c>
       <c r="P394" t="n">
-        <v>1486</v>
+        <v>1383</v>
       </c>
       <c r="Q394" t="n">
-        <v>1486</v>
+        <v>1383</v>
       </c>
       <c r="R394" t="n">
-        <v>14.86</v>
+        <v>13.83</v>
       </c>
       <c r="S394" t="n">
         <v>8</v>
@@ -27699,13 +27699,13 @@
         <v>3223</v>
       </c>
       <c r="P409" t="n">
-        <v>3299</v>
+        <v>3500</v>
       </c>
       <c r="Q409" t="n">
-        <v>3299</v>
+        <v>3500</v>
       </c>
       <c r="R409" t="n">
-        <v>32.99</v>
+        <v>35</v>
       </c>
       <c r="S409" t="n">
         <v>8</v>
@@ -28119,13 +28119,13 @@
         <v>3854</v>
       </c>
       <c r="P415" t="n">
-        <v>3609</v>
+        <v>4215</v>
       </c>
       <c r="Q415" t="n">
-        <v>3854</v>
+        <v>4215</v>
       </c>
       <c r="R415" t="n">
-        <v>38.54</v>
+        <v>42.15</v>
       </c>
       <c r="S415" t="n">
         <v>8</v>
@@ -30359,13 +30359,13 @@
         <v>4704</v>
       </c>
       <c r="P447" t="n">
-        <v>5077</v>
+        <v>5716</v>
       </c>
       <c r="Q447" t="n">
-        <v>5077</v>
+        <v>5716</v>
       </c>
       <c r="R447" t="n">
-        <v>50.57</v>
+        <v>56.94</v>
       </c>
       <c r="S447" t="n">
         <v>8</v>
@@ -30499,13 +30499,13 @@
         <v>4114</v>
       </c>
       <c r="P449" t="n">
-        <v>5598</v>
+        <v>6837</v>
       </c>
       <c r="Q449" t="n">
-        <v>5598</v>
+        <v>6837</v>
       </c>
       <c r="R449" t="n">
-        <v>55.98</v>
+        <v>68.37</v>
       </c>
       <c r="S449" t="n">
         <v>8</v>
@@ -30849,13 +30849,13 @@
         <v>6391</v>
       </c>
       <c r="P454" t="n">
-        <v>7740</v>
+        <v>6249</v>
       </c>
       <c r="Q454" t="n">
-        <v>7740</v>
+        <v>6391</v>
       </c>
       <c r="R454" t="n">
-        <v>77.40000000000001</v>
+        <v>63.91</v>
       </c>
       <c r="S454" t="n">
         <v>8</v>
@@ -31899,13 +31899,13 @@
         <v>2969</v>
       </c>
       <c r="P469" t="n">
-        <v>3423</v>
+        <v>5619</v>
       </c>
       <c r="Q469" t="n">
-        <v>3423</v>
+        <v>5619</v>
       </c>
       <c r="R469" t="n">
-        <v>42.79</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="S469" t="n">
         <v>8</v>
@@ -32109,13 +32109,13 @@
         <v>5733</v>
       </c>
       <c r="P472" t="n">
-        <v>6132</v>
+        <v>7796</v>
       </c>
       <c r="Q472" t="n">
-        <v>6132</v>
+        <v>7796</v>
       </c>
       <c r="R472" t="n">
-        <v>61.32</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="S472" t="n">
         <v>8</v>
@@ -33229,7 +33229,7 @@
         <v>905</v>
       </c>
       <c r="P488" t="n">
-        <v>930</v>
+        <v>957</v>
       </c>
       <c r="Q488" t="n">
         <v>958</v>
@@ -33789,13 +33789,13 @@
         <v>5058</v>
       </c>
       <c r="P496" t="n">
-        <v>5311</v>
+        <v>6431</v>
       </c>
       <c r="Q496" t="n">
-        <v>5311</v>
+        <v>6431</v>
       </c>
       <c r="R496" t="n">
-        <v>52.9</v>
+        <v>64.06</v>
       </c>
       <c r="S496" t="n">
         <v>8</v>
@@ -33929,13 +33929,13 @@
         <v>4963</v>
       </c>
       <c r="P498" t="n">
-        <v>5443</v>
+        <v>6149</v>
       </c>
       <c r="Q498" t="n">
-        <v>5443</v>
+        <v>6149</v>
       </c>
       <c r="R498" t="n">
-        <v>41.87</v>
+        <v>47.3</v>
       </c>
       <c r="S498" t="n">
         <v>8</v>
@@ -34629,13 +34629,13 @@
         <v>7115</v>
       </c>
       <c r="P508" t="n">
-        <v>7358</v>
+        <v>8280</v>
       </c>
       <c r="Q508" t="n">
-        <v>8169</v>
+        <v>8280</v>
       </c>
       <c r="R508" t="n">
-        <v>81.69</v>
+        <v>82.8</v>
       </c>
       <c r="S508" t="n">
         <v>8</v>
@@ -35049,7 +35049,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q514" t="n">
         <v>1</v>
@@ -35329,13 +35329,13 @@
         <v>4667</v>
       </c>
       <c r="P518" t="n">
-        <v>4666</v>
+        <v>4816</v>
       </c>
       <c r="Q518" t="n">
-        <v>4712</v>
+        <v>4816</v>
       </c>
       <c r="R518" t="n">
-        <v>47.12</v>
+        <v>48.16</v>
       </c>
       <c r="S518" t="n">
         <v>8</v>
@@ -35889,13 +35889,13 @@
         <v>4832</v>
       </c>
       <c r="P526" t="n">
-        <v>5604</v>
+        <v>5653</v>
       </c>
       <c r="Q526" t="n">
-        <v>5604</v>
+        <v>5653</v>
       </c>
       <c r="R526" t="n">
-        <v>62.27</v>
+        <v>62.81</v>
       </c>
       <c r="S526" t="n">
         <v>8</v>
@@ -36379,13 +36379,13 @@
         <v>665</v>
       </c>
       <c r="P533" t="n">
-        <v>919</v>
+        <v>876</v>
       </c>
       <c r="Q533" t="n">
-        <v>919</v>
+        <v>876</v>
       </c>
       <c r="R533" t="n">
-        <v>45.95</v>
+        <v>43.8</v>
       </c>
       <c r="S533" t="n">
         <v>8</v>
@@ -36495,7 +36495,7 @@
         <v>3366</v>
       </c>
       <c r="P535" t="n">
-        <v>3339</v>
+        <v>3485</v>
       </c>
       <c r="Q535" t="n">
         <v>4223</v>
@@ -36821,13 +36821,13 @@
         <v>4608</v>
       </c>
       <c r="P540" t="n">
-        <v>4605</v>
+        <v>4761</v>
       </c>
       <c r="Q540" t="n">
-        <v>4753</v>
+        <v>4761</v>
       </c>
       <c r="R540" t="n">
-        <v>39.61</v>
+        <v>39.68</v>
       </c>
       <c r="S540" t="n">
         <v>8</v>
@@ -36937,7 +36937,7 @@
         <v>435</v>
       </c>
       <c r="P542" t="n">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="Q542" t="n">
         <v>3755</v>
@@ -37007,7 +37007,7 @@
         <v>2804</v>
       </c>
       <c r="P543" t="n">
-        <v>824</v>
+        <v>688</v>
       </c>
       <c r="Q543" t="n">
         <v>5012</v>
@@ -37077,7 +37077,7 @@
         <v>5417</v>
       </c>
       <c r="P544" t="n">
-        <v>2663</v>
+        <v>2274</v>
       </c>
       <c r="Q544" t="n">
         <v>6510</v>
@@ -37147,7 +37147,7 @@
         <v>6861</v>
       </c>
       <c r="P545" t="n">
-        <v>2427</v>
+        <v>2154</v>
       </c>
       <c r="Q545" t="n">
         <v>6861</v>
@@ -37287,7 +37287,7 @@
         <v>6600</v>
       </c>
       <c r="P547" t="n">
-        <v>5751</v>
+        <v>5188</v>
       </c>
       <c r="Q547" t="n">
         <v>8472</v>
@@ -37357,7 +37357,7 @@
         <v>3233</v>
       </c>
       <c r="P548" t="n">
-        <v>2219</v>
+        <v>742</v>
       </c>
       <c r="Q548" t="n">
         <v>3752</v>
@@ -37427,7 +37427,7 @@
         <v>3810</v>
       </c>
       <c r="P549" t="n">
-        <v>791</v>
+        <v>610</v>
       </c>
       <c r="Q549" t="n">
         <v>3847</v>
@@ -37683,13 +37683,13 @@
         <v>2857</v>
       </c>
       <c r="P553" t="n">
-        <v>2840</v>
+        <v>3039</v>
       </c>
       <c r="Q553" t="n">
-        <v>2857</v>
+        <v>3039</v>
       </c>
       <c r="R553" t="n">
-        <v>57.14</v>
+        <v>60.78</v>
       </c>
       <c r="S553" t="n">
         <v>8</v>
@@ -37915,13 +37915,13 @@
         <v>1904</v>
       </c>
       <c r="P557" t="n">
-        <v>2338</v>
+        <v>3563</v>
       </c>
       <c r="Q557" t="n">
-        <v>2338</v>
+        <v>3563</v>
       </c>
       <c r="R557" t="n">
-        <v>11.69</v>
+        <v>17.82</v>
       </c>
       <c r="S557" t="n">
         <v>8</v>
@@ -38381,13 +38381,13 @@
         <v>3465</v>
       </c>
       <c r="P564" t="n">
-        <v>3466</v>
+        <v>3651</v>
       </c>
       <c r="Q564" t="n">
-        <v>3466</v>
+        <v>3651</v>
       </c>
       <c r="R564" t="n">
-        <v>57.77</v>
+        <v>60.85</v>
       </c>
       <c r="S564" t="n">
         <v>8</v>
@@ -38777,7 +38777,7 @@
         <v>3766</v>
       </c>
       <c r="P570" t="n">
-        <v>2623</v>
+        <v>2695</v>
       </c>
       <c r="Q570" t="n">
         <v>3836</v>
@@ -38847,13 +38847,13 @@
         <v>5101</v>
       </c>
       <c r="P571" t="n">
-        <v>6088</v>
+        <v>6670</v>
       </c>
       <c r="Q571" t="n">
-        <v>6088</v>
+        <v>6670</v>
       </c>
       <c r="R571" t="n">
-        <v>86.97</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="S571" t="n">
         <v>8</v>
@@ -38987,13 +38987,13 @@
         <v>4368</v>
       </c>
       <c r="P573" t="n">
-        <v>4456</v>
+        <v>4606</v>
       </c>
       <c r="Q573" t="n">
-        <v>4456</v>
+        <v>4606</v>
       </c>
       <c r="R573" t="n">
-        <v>67.55</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="S573" t="n">
         <v>8</v>
@@ -39943,13 +39943,13 @@
         <v>2423</v>
       </c>
       <c r="P587" t="n">
-        <v>1970</v>
+        <v>3744</v>
       </c>
       <c r="Q587" t="n">
-        <v>3670</v>
+        <v>3744</v>
       </c>
       <c r="R587" t="n">
-        <v>36.7</v>
+        <v>37.44</v>
       </c>
       <c r="S587" t="n">
         <v>8</v>
@@ -40293,7 +40293,7 @@
         <v>398</v>
       </c>
       <c r="P592" t="n">
-        <v>349</v>
+        <v>92</v>
       </c>
       <c r="Q592" t="n">
         <v>398</v>
@@ -40853,13 +40853,13 @@
         <v>5124</v>
       </c>
       <c r="P600" t="n">
-        <v>7646</v>
+        <v>7268</v>
       </c>
       <c r="Q600" t="n">
-        <v>7646</v>
+        <v>7268</v>
       </c>
       <c r="R600" t="n">
-        <v>76.45999999999999</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="S600" t="n">
         <v>8</v>
@@ -41133,13 +41133,13 @@
         <v>6402</v>
       </c>
       <c r="P604" t="n">
-        <v>8600</v>
+        <v>7580</v>
       </c>
       <c r="Q604" t="n">
-        <v>8600</v>
+        <v>7580</v>
       </c>
       <c r="R604" t="n">
-        <v>66.15000000000001</v>
+        <v>58.31</v>
       </c>
       <c r="S604" t="n">
         <v>8</v>
@@ -42485,7 +42485,7 @@
         <v>4097</v>
       </c>
       <c r="P624" t="n">
-        <v>3993</v>
+        <v>3527</v>
       </c>
       <c r="Q624" t="n">
         <v>5528</v>
@@ -43185,13 +43185,13 @@
         <v>447</v>
       </c>
       <c r="P634" t="n">
-        <v>334</v>
+        <v>942</v>
       </c>
       <c r="Q634" t="n">
-        <v>641</v>
+        <v>942</v>
       </c>
       <c r="R634" t="n">
-        <v>10.68</v>
+        <v>15.7</v>
       </c>
       <c r="S634" t="n">
         <v>8</v>
@@ -43465,7 +43465,7 @@
         <v>7248</v>
       </c>
       <c r="P638" t="n">
-        <v>4823</v>
+        <v>4412</v>
       </c>
       <c r="Q638" t="n">
         <v>9088</v>
@@ -43535,13 +43535,13 @@
         <v>7734</v>
       </c>
       <c r="P639" t="n">
-        <v>7593</v>
+        <v>8908</v>
       </c>
       <c r="Q639" t="n">
-        <v>8193</v>
+        <v>8908</v>
       </c>
       <c r="R639" t="n">
-        <v>85.69</v>
+        <v>93.17</v>
       </c>
       <c r="S639" t="n">
         <v>8</v>
@@ -44305,13 +44305,13 @@
         <v>2379</v>
       </c>
       <c r="P650" t="n">
-        <v>2361</v>
+        <v>2390</v>
       </c>
       <c r="Q650" t="n">
-        <v>2379</v>
+        <v>2390</v>
       </c>
       <c r="R650" t="n">
-        <v>29.74</v>
+        <v>29.88</v>
       </c>
       <c r="S650" t="n">
         <v>8</v>
@@ -44445,7 +44445,7 @@
         <v>2179</v>
       </c>
       <c r="P652" t="n">
-        <v>2151</v>
+        <v>2780</v>
       </c>
       <c r="Q652" t="n">
         <v>2801</v>
@@ -44515,7 +44515,7 @@
         <v>2204</v>
       </c>
       <c r="P653" t="n">
-        <v>2140</v>
+        <v>2164</v>
       </c>
       <c r="Q653" t="n">
         <v>2204</v>
@@ -45821,7 +45821,7 @@
         <v>4216</v>
       </c>
       <c r="P672" t="n">
-        <v>2632</v>
+        <v>3585</v>
       </c>
       <c r="Q672" t="n">
         <v>5639</v>
@@ -45891,13 +45891,13 @@
         <v>2439</v>
       </c>
       <c r="P673" t="n">
-        <v>3098</v>
+        <v>3083</v>
       </c>
       <c r="Q673" t="n">
-        <v>3098</v>
+        <v>3083</v>
       </c>
       <c r="R673" t="n">
-        <v>25.82</v>
+        <v>25.69</v>
       </c>
       <c r="S673" t="n">
         <v>8</v>
@@ -46031,13 +46031,13 @@
         <v>3710</v>
       </c>
       <c r="P675" t="n">
-        <v>3893</v>
+        <v>3955</v>
       </c>
       <c r="Q675" t="n">
-        <v>3893</v>
+        <v>3955</v>
       </c>
       <c r="R675" t="n">
-        <v>77.86</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="S675" t="n">
         <v>8</v>
@@ -46521,7 +46521,7 @@
         <v>4565</v>
       </c>
       <c r="P682" t="n">
-        <v>3615</v>
+        <v>4536</v>
       </c>
       <c r="Q682" t="n">
         <v>5228</v>
@@ -46893,13 +46893,13 @@
         <v>372</v>
       </c>
       <c r="P688" t="n">
-        <v>385</v>
+        <v>932</v>
       </c>
       <c r="Q688" t="n">
-        <v>385</v>
+        <v>932</v>
       </c>
       <c r="R688" t="n">
-        <v>8.949999999999999</v>
+        <v>21.67</v>
       </c>
       <c r="S688" t="n">
         <v>8</v>
@@ -47803,13 +47803,13 @@
         <v>266</v>
       </c>
       <c r="P701" t="n">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="Q701" t="n">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="R701" t="n">
-        <v>6.9</v>
+        <v>7.02</v>
       </c>
       <c r="S701" t="n">
         <v>8</v>
@@ -47873,13 +47873,13 @@
         <v>2843</v>
       </c>
       <c r="P702" t="n">
-        <v>2632</v>
+        <v>2954</v>
       </c>
       <c r="Q702" t="n">
-        <v>2843</v>
+        <v>2954</v>
       </c>
       <c r="R702" t="n">
-        <v>40.61</v>
+        <v>42.2</v>
       </c>
       <c r="S702" t="n">
         <v>8</v>
@@ -48013,7 +48013,7 @@
         <v>400</v>
       </c>
       <c r="P704" t="n">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="Q704" t="n">
         <v>410</v>
@@ -48083,7 +48083,7 @@
         <v>3176</v>
       </c>
       <c r="P705" t="n">
-        <v>1030</v>
+        <v>1082</v>
       </c>
       <c r="Q705" t="n">
         <v>3176</v>
@@ -48503,7 +48503,7 @@
         <v>4</v>
       </c>
       <c r="P711" t="n">
-        <v>-56</v>
+        <v>-50</v>
       </c>
       <c r="Q711" t="n">
         <v>4528</v>
@@ -48713,13 +48713,13 @@
         <v>9341</v>
       </c>
       <c r="P714" t="n">
-        <v>7740</v>
+        <v>9639</v>
       </c>
       <c r="Q714" t="n">
-        <v>9341</v>
+        <v>9639</v>
       </c>
       <c r="R714" t="n">
-        <v>87.3</v>
+        <v>90.08</v>
       </c>
       <c r="S714" t="n">
         <v>8</v>
@@ -48923,13 +48923,13 @@
         <v>1355</v>
       </c>
       <c r="P717" t="n">
-        <v>1276</v>
+        <v>1627</v>
       </c>
       <c r="Q717" t="n">
-        <v>1486</v>
+        <v>1627</v>
       </c>
       <c r="R717" t="n">
-        <v>14.8</v>
+        <v>16.21</v>
       </c>
       <c r="S717" t="n">
         <v>8</v>
@@ -49273,7 +49273,7 @@
         <v>4643</v>
       </c>
       <c r="P722" t="n">
-        <v>4352</v>
+        <v>4422</v>
       </c>
       <c r="Q722" t="n">
         <v>4643</v>
@@ -49903,7 +49903,7 @@
         <v>6867</v>
       </c>
       <c r="P731" t="n">
-        <v>6286</v>
+        <v>6562</v>
       </c>
       <c r="Q731" t="n">
         <v>7742</v>
@@ -50533,7 +50533,7 @@
         <v>8830</v>
       </c>
       <c r="P740" t="n">
-        <v>6506</v>
+        <v>5581</v>
       </c>
       <c r="Q740" t="n">
         <v>8830</v>
@@ -50603,13 +50603,13 @@
         <v>1267</v>
       </c>
       <c r="P741" t="n">
-        <v>1400</v>
+        <v>1746</v>
       </c>
       <c r="Q741" t="n">
-        <v>1610</v>
+        <v>1746</v>
       </c>
       <c r="R741" t="n">
-        <v>13.42</v>
+        <v>14.55</v>
       </c>
       <c r="S741" t="n">
         <v>8</v>
@@ -50673,7 +50673,7 @@
         <v>6356</v>
       </c>
       <c r="P742" t="n">
-        <v>7070</v>
+        <v>6822</v>
       </c>
       <c r="Q742" t="n">
         <v>11079</v>
@@ -50813,7 +50813,7 @@
         <v>3932</v>
       </c>
       <c r="P744" t="n">
-        <v>4043</v>
+        <v>4054</v>
       </c>
       <c r="Q744" t="n">
         <v>5457</v>
@@ -50883,7 +50883,7 @@
         <v>7046</v>
       </c>
       <c r="P745" t="n">
-        <v>6620</v>
+        <v>6912</v>
       </c>
       <c r="Q745" t="n">
         <v>7787</v>
@@ -50953,7 +50953,7 @@
         <v>2365</v>
       </c>
       <c r="P746" t="n">
-        <v>2986</v>
+        <v>2753</v>
       </c>
       <c r="Q746" t="n">
         <v>4293</v>
@@ -51023,7 +51023,7 @@
         <v>4170</v>
       </c>
       <c r="P747" t="n">
-        <v>3820</v>
+        <v>4002</v>
       </c>
       <c r="Q747" t="n">
         <v>5747</v>
@@ -51093,7 +51093,7 @@
         <v>5858</v>
       </c>
       <c r="P748" t="n">
-        <v>4788</v>
+        <v>4821</v>
       </c>
       <c r="Q748" t="n">
         <v>5858</v>
@@ -51163,7 +51163,7 @@
         <v>5114</v>
       </c>
       <c r="P749" t="n">
-        <v>2143</v>
+        <v>1882</v>
       </c>
       <c r="Q749" t="n">
         <v>5114</v>
@@ -51233,7 +51233,7 @@
         <v>1154</v>
       </c>
       <c r="P750" t="n">
-        <v>1089</v>
+        <v>877</v>
       </c>
       <c r="Q750" t="n">
         <v>1431</v>
@@ -51443,13 +51443,13 @@
         <v>1934</v>
       </c>
       <c r="P753" t="n">
-        <v>3412</v>
+        <v>3352</v>
       </c>
       <c r="Q753" t="n">
-        <v>3412</v>
+        <v>3352</v>
       </c>
       <c r="R753" t="n">
-        <v>42.65</v>
+        <v>41.9</v>
       </c>
       <c r="S753" t="n">
         <v>8</v>
@@ -54029,7 +54029,7 @@
         <v>1241</v>
       </c>
       <c r="P792" t="n">
-        <v>325</v>
+        <v>1699</v>
       </c>
       <c r="Q792" t="n">
         <v>1907</v>
@@ -54309,13 +54309,13 @@
         <v>3990</v>
       </c>
       <c r="P796" t="n">
-        <v>4057</v>
+        <v>4082</v>
       </c>
       <c r="Q796" t="n">
-        <v>4057</v>
+        <v>4082</v>
       </c>
       <c r="R796" t="n">
-        <v>40.57</v>
+        <v>40.82</v>
       </c>
       <c r="S796" t="n">
         <v>8</v>
@@ -55335,7 +55335,7 @@
         <v>128</v>
       </c>
       <c r="P811" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q811" t="n">
         <v>4173</v>
@@ -56077,13 +56077,13 @@
         <v>5628</v>
       </c>
       <c r="P824" t="n">
-        <v>5802</v>
+        <v>5870</v>
       </c>
       <c r="Q824" t="n">
-        <v>5802</v>
+        <v>5870</v>
       </c>
       <c r="R824" t="n">
-        <v>95.19</v>
+        <v>96.31</v>
       </c>
       <c r="S824" t="n">
         <v>8</v>
@@ -56287,13 +56287,13 @@
         <v>7717</v>
       </c>
       <c r="P827" t="n">
-        <v>7874</v>
+        <v>8001</v>
       </c>
       <c r="Q827" t="n">
-        <v>7907</v>
+        <v>8001</v>
       </c>
       <c r="R827" t="n">
-        <v>88.20999999999999</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="S827" t="n">
         <v>8</v>
@@ -56427,13 +56427,13 @@
         <v>7806</v>
       </c>
       <c r="P829" t="n">
-        <v>6618</v>
+        <v>9400</v>
       </c>
       <c r="Q829" t="n">
-        <v>7806</v>
+        <v>9400</v>
       </c>
       <c r="R829" t="n">
-        <v>65.05</v>
+        <v>78.33</v>
       </c>
       <c r="S829" t="n">
         <v>8</v>
@@ -56497,7 +56497,7 @@
         <v>258</v>
       </c>
       <c r="P830" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q830" t="n">
         <v>3542</v>
@@ -56567,13 +56567,13 @@
         <v>7814</v>
       </c>
       <c r="P831" t="n">
-        <v>7948</v>
+        <v>8116</v>
       </c>
       <c r="Q831" t="n">
-        <v>7948</v>
+        <v>8116</v>
       </c>
       <c r="R831" t="n">
-        <v>55.58</v>
+        <v>56.76</v>
       </c>
       <c r="S831" t="n">
         <v>8</v>
@@ -56637,13 +56637,13 @@
         <v>1722</v>
       </c>
       <c r="P832" t="n">
-        <v>1642</v>
+        <v>1749</v>
       </c>
       <c r="Q832" t="n">
-        <v>1722</v>
+        <v>1749</v>
       </c>
       <c r="R832" t="n">
-        <v>19.13</v>
+        <v>19.43</v>
       </c>
       <c r="S832" t="n">
         <v>8</v>
@@ -58317,7 +58317,7 @@
         <v>10395</v>
       </c>
       <c r="P856" t="n">
-        <v>9232</v>
+        <v>9640</v>
       </c>
       <c r="Q856" t="n">
         <v>10395</v>
@@ -59085,7 +59085,7 @@
         <v>5274</v>
       </c>
       <c r="P868" t="n">
-        <v>3737</v>
+        <v>3760</v>
       </c>
       <c r="Q868" t="n">
         <v>8343</v>
